--- a/Result/profitability/3149.xlsx
+++ b/Result/profitability/3149.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5475</v>
+        <v>-0.57375</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.106250000000001</v>
+        <v>-4.96625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-1.11</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6525</v>
+        <v>-0.6075</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.470000000000001</v>
+        <v>-5.51875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.645</v>
+        <v>-0.6074999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.0575</v>
+        <v>-3.39875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5950000000000001</v>
+        <v>-0.555</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.29</v>
+        <v>-1.615</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.49375</v>
+        <v>-0.4687500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6612500000000001</v>
+        <v>0.9525</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3562500000000001</v>
+        <v>-0.3325</v>
       </c>
       <c r="N7" t="n">
-        <v>4.2</v>
+        <v>5.342499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.06250000000000006</v>
+        <v>-0.07625000000000004</v>
       </c>
       <c r="N8" t="n">
-        <v>9.695</v>
+        <v>9.80875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>3149</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>554</v>
+      </c>
+      <c r="D71" t="n">
+        <v>572</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-18</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-19.28%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-108</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-108</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-0.6112500000000001</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-7.202500000000001</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.2972972972972974</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.9099999999999997</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.2198067632850241</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.6257242178447278</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
